--- a/runs/KO/2026-10-13/bear/scratch/gen_wo_tg3/dcf.xlsx
+++ b/runs/KO/2026-10-13/bear/scratch/gen_wo_tg3/dcf.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.04576473262145622</v>
+        <v>0.04576473262145623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0.03</v>
@@ -1018,7 +1018,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>52862.02214222582</v>
+        <v>52363.32382012936</v>
       </c>
     </row>
     <row r="4">
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>17545.43376922617</v>
+        <v>17379.91080913914</v>
       </c>
     </row>
     <row r="6">
@@ -1240,7 +1240,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>13300.98841902524</v>
+        <v>13175.50739620425</v>
       </c>
     </row>
     <row r="12">
@@ -1351,7 +1351,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>10004.2582803355</v>
+        <v>9909.878485237996</v>
       </c>
     </row>
     <row r="16">
@@ -1419,7 +1419,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>53701.97370499204</v>
+        <v>53153.81606243531</v>
       </c>
     </row>
     <row r="21">
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="C21" s="4" t="n">
-        <v>13421.91486513105</v>
+        <v>13295.29302678076</v>
       </c>
     </row>
     <row r="22">
@@ -1447,7 +1447,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>296021.1119438153</v>
+        <v>293228.4599443454</v>
       </c>
     </row>
     <row r="23">
@@ -1461,7 +1461,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>222650.4953633413</v>
+        <v>220550.0189919891</v>
       </c>
     </row>
     <row r="24">
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>276352.4690683333</v>
+        <v>273703.8350544244</v>
       </c>
     </row>
     <row r="25">
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>296763.9690683333</v>
+        <v>294115.3350544244</v>
       </c>
     </row>
     <row r="27">
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>303276.5565822307</v>
+        <v>300490.4292446193</v>
       </c>
     </row>
     <row r="28">
@@ -1531,7 +1531,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>70.4966426272038</v>
+        <v>69.84900726281249</v>
       </c>
     </row>
     <row r="29">
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="C29" s="6" t="n">
-        <v>-0.2177469987</v>
+        <v>-0.2249333651</v>
       </c>
     </row>
   </sheetData>
